--- a/win台机/GTG_青春小馆定时自动发布/定时配置.xlsx
+++ b/win台机/GTG_青春小馆定时自动发布/定时配置.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
